--- a/public/excel/products.xlsx
+++ b/public/excel/products.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web-dev\Текущий проекты\truck-import\public\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web-dev\now-projects\truck-import\public\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16F683F-A73D-4E96-97F3-CDBFFF46704B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F220D3-3CF3-4ABD-BBBE-094979D49C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20940" yWindow="1884" windowWidth="17424" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20124" yWindow="2700" windowWidth="17424" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="можешь мне сгенерировать такой " sheetId="1" r:id="rId1"/>
@@ -67,9 +67,6 @@
     <t>Летняя шина для легковых автомобилей</t>
   </si>
   <si>
-    <t>Диаметр&gt;R17, Сезонность&gt;Лето</t>
-  </si>
-  <si>
     <t>Диски Replica BMW Style 666</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>Литые диски для BMW M3/M4</t>
   </si>
   <si>
-    <t>Цвет&gt;Черный глянцевый, Материал&gt;Алюминий</t>
-  </si>
-  <si>
     <t>Масло моторное Castrol Edge 5W-30</t>
   </si>
   <si>
@@ -106,9 +100,6 @@
     <t>Синтетическое моторное масло</t>
   </si>
   <si>
-    <t>Объем&gt;4л, Вязкость&gt;5W-30, Тип&gt;Синтетика</t>
-  </si>
-  <si>
     <t>Тормозные колодки Brembo P 06 088</t>
   </si>
   <si>
@@ -124,9 +115,6 @@
     <t>Передние колодки для BMW F30</t>
   </si>
   <si>
-    <t>Материал&gt;Керамика, Назначение&gt;Дорога</t>
-  </si>
-  <si>
     <t>Свечи зажигания NGK Iridium</t>
   </si>
   <si>
@@ -142,9 +130,6 @@
     <t>Иридиевые свечи для лучшей искры</t>
   </si>
   <si>
-    <t>Зазор&gt;0.8мм, Срок службы&gt;100000км</t>
-  </si>
-  <si>
     <t>ОШИБКА: Дубликат артикула</t>
   </si>
   <si>
@@ -226,9 +211,6 @@
     <t>Зеркало заднего вида правое</t>
   </si>
   <si>
-    <t>Тип&gt;Электрическое, Цвет&gt;Черный</t>
-  </si>
-  <si>
     <t>3 дня</t>
   </si>
   <si>
@@ -254,6 +236,24 @@
   </si>
   <si>
     <t>б</t>
+  </si>
+  <si>
+    <t>Диаметр&gt;R17; Сезонность&gt;Лето</t>
+  </si>
+  <si>
+    <t>Цвет&gt;Черный глянцевый; Материал&gt;Алюминий</t>
+  </si>
+  <si>
+    <t>Объем&gt;4л; Вязкость&gt;5W-30; Тип&gt;Синтетика</t>
+  </si>
+  <si>
+    <t>Материал&gt;Керамика; Назначение&gt;Дорога</t>
+  </si>
+  <si>
+    <t>Зазор&gt;0.8мм; Срок службы&gt;100000км</t>
+  </si>
+  <si>
+    <t>Тип&gt;Электрическое; Цвет&gt;Черный</t>
   </si>
 </sst>
 </file>
@@ -519,6 +519,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.26953125" customWidth="1"/>
+    <col min="9" max="9" width="36.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -573,18 +574,18 @@
         <v>14</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C3" s="1">
         <v>800</v>
@@ -593,56 +594,56 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D4" s="1">
         <v>200</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1">
         <v>120</v>
@@ -651,27 +652,27 @@
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1">
         <v>15</v>
@@ -680,24 +681,24 @@
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
@@ -715,41 +716,41 @@
         <v>13</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1">
         <v>25</v>
@@ -758,22 +759,22 @@
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1">
         <v>30</v>
@@ -782,50 +783,50 @@
         <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1">
         <v>45</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1">
         <v>75</v>
@@ -834,19 +835,19 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H12" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/public/excel/products.xlsx
+++ b/public/excel/products.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Web-dev\now-projects\truck-import\public\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F220D3-3CF3-4ABD-BBBE-094979D49C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7196D378-2B54-4D88-8F3D-90AC81AAA96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20124" yWindow="2700" windowWidth="17424" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="можешь мне сгенерировать такой " sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>Название товара</t>
   </si>
@@ -37,9 +37,6 @@
     <t>Бренд</t>
   </si>
   <si>
-    <t>Категория</t>
-  </si>
-  <si>
     <t>Описание</t>
   </si>
   <si>
@@ -61,9 +58,6 @@
     <t>Continental</t>
   </si>
   <si>
-    <t>Шины&gt;Летние</t>
-  </si>
-  <si>
     <t>Летняя шина для легковых автомобилей</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>Replica</t>
   </si>
   <si>
-    <t>BMW&gt;Диски</t>
-  </si>
-  <si>
     <t>Литые диски для BMW M3/M4</t>
   </si>
   <si>
@@ -94,9 +85,6 @@
     <t>Castrol</t>
   </si>
   <si>
-    <t>Масла&gt;Моторные</t>
-  </si>
-  <si>
     <t>Синтетическое моторное масло</t>
   </si>
   <si>
@@ -109,9 +97,6 @@
     <t>Brembo</t>
   </si>
   <si>
-    <t>BMW&gt;Тормоза</t>
-  </si>
-  <si>
     <t>Передние колодки для BMW F30</t>
   </si>
   <si>
@@ -124,9 +109,6 @@
     <t>NGK</t>
   </si>
   <si>
-    <t>Запчасти&gt;Электрика</t>
-  </si>
-  <si>
     <t>Иридиевые свечи для лучшей искры</t>
   </si>
   <si>
@@ -145,9 +127,6 @@
     <t>Bosch</t>
   </si>
   <si>
-    <t>Запчасти&gt;Фильтры</t>
-  </si>
-  <si>
     <t>Фильтр воздушный</t>
   </si>
   <si>
@@ -172,9 +151,6 @@
     <t>Denso</t>
   </si>
   <si>
-    <t>Свечи&gt;Накаливания</t>
-  </si>
-  <si>
     <t>Свечи накаливания</t>
   </si>
   <si>
@@ -184,15 +160,9 @@
     <t>BAD-QTY-003</t>
   </si>
   <si>
-    <t>ABC</t>
-  </si>
-  <si>
     <t>KYB</t>
   </si>
   <si>
-    <t>Амортизаторы&gt;Передние</t>
-  </si>
-  <si>
     <t>Передний амортизатор</t>
   </si>
   <si>
@@ -205,9 +175,6 @@
     <t>VAG</t>
   </si>
   <si>
-    <t>Mercedes&gt;Кузов</t>
-  </si>
-  <si>
     <t>Зеркало заднего вида правое</t>
   </si>
   <si>
@@ -254,6 +221,39 @@
   </si>
   <si>
     <t>Тип&gt;Электрическое; Цвет&gt;Черный</t>
+  </si>
+  <si>
+    <t>Тип детали</t>
+  </si>
+  <si>
+    <t>Шины</t>
+  </si>
+  <si>
+    <t>Диски</t>
+  </si>
+  <si>
+    <t>Масла</t>
+  </si>
+  <si>
+    <t>Тормоза</t>
+  </si>
+  <si>
+    <t>Электрика</t>
+  </si>
+  <si>
+    <t>Фильтры</t>
+  </si>
+  <si>
+    <t>Амортизаторы</t>
+  </si>
+  <si>
+    <t>Кузов</t>
+  </si>
+  <si>
+    <t>Совместимость</t>
+  </si>
+  <si>
+    <t>BMW; Audi; Mercedes</t>
   </si>
 </sst>
 </file>
@@ -515,14 +515,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.26953125" customWidth="1"/>
-    <col min="9" max="9" width="36.453125" customWidth="1"/>
+    <col min="6" max="6" width="19.6328125" customWidth="1"/>
+    <col min="7" max="7" width="21.36328125" customWidth="1"/>
+    <col min="8" max="8" width="45.1796875" customWidth="1"/>
+    <col min="9" max="9" width="18.54296875" customWidth="1"/>
+    <col min="10" max="10" width="42.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -539,53 +543,59 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="D2" s="1">
         <v>50</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="C3" s="1">
         <v>800</v>
@@ -594,56 +604,62 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="D4" s="1">
         <v>200</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C5" s="1">
         <v>120</v>
@@ -652,27 +668,30 @@
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
+      </c>
+      <c r="G5" t="s">
+        <v>77</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1">
         <v>15</v>
@@ -681,27 +700,30 @@
         <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="1">
         <v>160</v>
@@ -710,47 +732,53 @@
         <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C9" s="1">
         <v>25</v>
@@ -759,22 +787,25 @@
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>77</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1">
         <v>30</v>
@@ -783,50 +814,56 @@
         <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="G10" t="s">
+        <v>77</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C11" s="1">
         <v>45</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>54</v>
+      <c r="D11" s="1">
+        <v>40</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1">
         <v>75</v>
@@ -835,19 +872,22 @@
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>77</v>
+      <c r="J12" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
